--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484286_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484286_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5889</v>
+        <v>4.5077</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2571</v>
+        <v>1.1759</v>
       </c>
       <c r="F2" t="n">
         <v>3.3319</v>
@@ -610,10 +610,10 @@
         <v>3.3208</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2834</v>
+        <v>-0.3646</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0305</v>
+        <v>-0.0507</v>
       </c>
       <c r="U2" t="n">
         <v>-0.3139</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4088</v>
+        <v>1.8865</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9519</v>
+        <v>0.2934</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4569</v>
+        <v>1.5931</v>
       </c>
       <c r="G3" t="n">
         <v>3.0462</v>
@@ -688,13 +688,13 @@
         <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0388</v>
+        <v>0.5165</v>
       </c>
       <c r="T3" t="n">
-        <v>2.537</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4982</v>
+        <v>-0.362</v>
       </c>
       <c r="V3" t="n">
         <v>0.2772</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2132</v>
+        <v>-0.0457</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.9895</v>
+        <v>-0.2212</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2027</v>
+        <v>0.1755</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1976</v>
+        <v>0.6158</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5887</v>
+        <v>0.4405</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.391</v>
+        <v>0.1753</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9213</v>
+        <v>0.0814</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4131</v>
+        <v>0.0409</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3344</v>
+        <v>0.0405</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1189</v>
+        <v>0.5344</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1755</v>
+        <v>0.3996</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9433</v>
+        <v>0.1348</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3514</v>
+        <v>-0.2242</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4153</v>
+        <v>-0.3026</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7668</v>
+        <v>0.0784</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0549</v>
+        <v>-1.2186</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2224</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.294</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2212</v>
+        <v>-2.0437</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1483</v>
+        <v>1.7497</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6158</v>
+        <v>-1.792</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4405</v>
+        <v>-0.2553</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1753</v>
+        <v>-1.5367</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0814</v>
+        <v>-0.9487</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0409</v>
+        <v>1.1269</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0405</v>
+        <v>-2.0756</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5344</v>
+        <v>-0.8433</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3996</v>
+        <v>-1.3822</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1348</v>
+        <v>0.5389</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7814</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q5" t="n">
+        <v>-4.1022</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.1534</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.2069</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3.2141</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.2141</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.7814</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.2515</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.3026</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.0511</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-1.2186</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1.2186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. VERA CUSCOLL</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0085</v>
+        <v>-0.3254</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0401</v>
+        <v>-3.929</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9684</v>
+        <v>3.6035</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1553</v>
+        <v>0.1976</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1553</v>
+        <v>0.5887</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.391</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0205</v>
+        <v>-0.9213</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0205</v>
+        <v>0.4131</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.3344</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1348</v>
+        <v>1.1189</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1348</v>
+        <v>0.1755</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1953</v>
+        <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1953</v>
+        <v>-0.1872</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0605</v>
+        <v>-0.3548</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1348</v>
+        <v>0.1676</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1638</v>
+        <v>0.0549</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1638</v>
+        <v>-0.2224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1813</v>
+        <v>-0.7745</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2013</v>
+        <v>-0.7835</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9799</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3969</v>
+        <v>-0.1075</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2617</v>
+        <v>-0.957</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1352</v>
+        <v>0.8496</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0409</v>
+        <v>-0.0682</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0409</v>
+        <v>0.0255</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4379</v>
+        <v>-0.0392</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3026</v>
+        <v>-0.9826</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1352</v>
+        <v>0.9433</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>2.5395</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2532</v>
+        <v>-0.8158</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2888</v>
+        <v>-0.1526</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0357</v>
+        <v>-0.6633</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6642</v>
+        <v>-1.2186</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5545</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>E. VERA CUSCOLL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2202</v>
+        <v>-0.9074</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6703</v>
+        <v>0.0611</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4501</v>
+        <v>-0.9684</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.792</v>
+        <v>0.1553</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2553</v>
+        <v>0.1553</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5367</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9487</v>
+        <v>0.0205</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1269</v>
+        <v>0.0205</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0756</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8433</v>
+        <v>0.1348</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3822</v>
+        <v>0.1348</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5389</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.1022</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5395</v>
+        <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0796</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8335</v>
+        <v>0.0406</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2461</v>
+        <v>-0.1348</v>
       </c>
       <c r="V8" t="n">
-        <v>3.2141</v>
+        <v>-1.1638</v>
       </c>
       <c r="W8" t="n">
-        <v>3.2141</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3156</v>
+        <v>-0.913</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1068</v>
+        <v>0.2031</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2089</v>
+        <v>-1.1161</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1075</v>
+        <v>-1.3969</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.957</v>
+        <v>-1.2617</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8496</v>
+        <v>-0.1352</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0682</v>
+        <v>0.0409</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0255</v>
+        <v>0.0409</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0392</v>
+        <v>-1.4379</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9826</v>
+        <v>-1.3026</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9433</v>
+        <v>-0.1352</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5395</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.357</v>
+        <v>0.0151</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4758</v>
+        <v>0.1156</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8811</v>
+        <v>-0.1005</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8279</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7854</v>
+        <v>-1.3338</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3383</v>
+        <v>-3.9139</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5529</v>
+        <v>2.5801</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2473</v>
@@ -1234,13 +1234,13 @@
         <v>2.9301</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4043</v>
+        <v>-0.9527</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.271</v>
+        <v>-0.8466</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1334</v>
+        <v>-0.1061</v>
       </c>
       <c r="V10" t="n">
         <v>2.9917</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7948</v>
+        <v>-6.3631</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2919</v>
+        <v>-2.8874</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5029</v>
+        <v>-3.4757</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3399</v>
@@ -1312,13 +1312,13 @@
         <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4001</v>
+        <v>0.0316</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0467</v>
+        <v>0.3577</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3533</v>
+        <v>-0.3261</v>
       </c>
       <c r="V11" t="n">
         <v>-3.7107</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.167800000000001</v>
+        <v>-4.5627</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.6504</v>
+        <v>-12.0452</v>
       </c>
       <c r="F12" t="n">
-        <v>7.482700000000001</v>
+        <v>7.4826</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2996000000000001</v>
+        <v>0.2995999999999996</v>
       </c>
       <c r="H12" t="n">
         <v>-1.0475</v>
@@ -1390,10 +1390,10 @@
         <v>18.5576</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.8342</v>
+        <v>-2.2289</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1267</v>
+        <v>-0.5218</v>
       </c>
       <c r="U12" t="n">
         <v>-1.7072</v>
@@ -1405,7 +1405,7 @@
         <v>9.697100000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.423599999999999</v>
+        <v>-8.4236</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4921</v>
+        <v>5.7119</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2667</v>
+        <v>2.379</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2254</v>
+        <v>3.333</v>
       </c>
       <c r="G13" t="n">
         <v>2.3502</v>
@@ -1468,13 +1468,13 @@
         <v>3.9069</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9949</v>
+        <v>0.225</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1691</v>
+        <v>-0.0569</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1743</v>
+        <v>0.2818</v>
       </c>
       <c r="V13" t="n">
         <v>2.16</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0209</v>
+        <v>4.2684</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0866</v>
+        <v>0.2167</v>
       </c>
       <c r="F14" t="n">
-        <v>4.1075</v>
+        <v>4.0517</v>
       </c>
       <c r="G14" t="n">
         <v>3.6458</v>
@@ -1546,13 +1546,13 @@
         <v>3.5162</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5938</v>
+        <v>0.8413</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.374</v>
+        <v>-0.0706</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9677</v>
+        <v>0.9119</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6093</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4639</v>
+        <v>2.5038</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.7297</v>
+        <v>0.0206</v>
       </c>
       <c r="F15" t="n">
-        <v>4.1936</v>
+        <v>2.4831</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7298</v>
+        <v>-0.339</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7701</v>
+        <v>-0.1507</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0403</v>
+        <v>-0.1883</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5608</v>
+        <v>-0.1748</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0728</v>
+        <v>0.5526</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.7274</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.169</v>
+        <v>-0.1641</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8429</v>
+        <v>-0.7032</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.5391</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.1488</v>
       </c>
       <c r="R15" t="n">
-        <v>3.3208</v>
+        <v>2.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0217</v>
+        <v>-0.2662</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0347</v>
+        <v>-0.2606</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9869</v>
+        <v>-0.0056</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.3276</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0549</v>
+        <v>2.6048</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0549</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7156</v>
+        <v>1.4953</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6872</v>
+        <v>-2.2353</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4028</v>
+        <v>3.7306</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.339</v>
+        <v>-0.7298</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1507</v>
+        <v>-0.7701</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1883</v>
+        <v>0.0403</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1748</v>
+        <v>-0.5608</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5526</v>
+        <v>0.0728</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7274</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1641</v>
+        <v>-0.169</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7032</v>
+        <v>-0.8429</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5391</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.1488</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9301</v>
+        <v>3.3208</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0544</v>
+        <v>1.0531</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9684</v>
+        <v>0.5292</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0.5239</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3276</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.6048</v>
+        <v>-0.0549</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6558</v>
+        <v>1.2029</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2488</v>
+        <v>1.5521</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.593</v>
+        <v>-0.3492</v>
       </c>
       <c r="G17" t="n">
         <v>-1.3426</v>
@@ -1780,13 +1780,13 @@
         <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5877</v>
+        <v>-0.0406</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3494</v>
+        <v>-0.046</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2383</v>
+        <v>0.0054</v>
       </c>
       <c r="V17" t="n">
         <v>1.2186</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6045</v>
+        <v>0.694</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1398</v>
+        <v>-0.2409</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7443</v>
+        <v>0.9349</v>
       </c>
       <c r="G18" t="n">
         <v>1.5123</v>
@@ -1858,13 +1858,13 @@
         <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0336</v>
+        <v>0.1231</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4458</v>
+        <v>0.3447</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4122</v>
+        <v>-0.2215</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9414</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4029</v>
+        <v>-0.22</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1801</v>
+        <v>0.2812</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.583</v>
+        <v>-0.5013</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1314</v>
@@ -1936,13 +1936,13 @@
         <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2481</v>
+        <v>-0.0653</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1678</v>
+        <v>-0.0667</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0803</v>
+        <v>0.0014</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6093</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-1.0913</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8377</v>
+        <v>-2.5455</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2908</v>
+        <v>1.4542</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0283</v>
@@ -2014,13 +2014,13 @@
         <v>2.5395</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8052</v>
+        <v>0.2608</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3374</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5322</v>
+        <v>-0.3688</v>
       </c>
       <c r="V20" t="n">
         <v>-0.8865</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9529</v>
+        <v>-3.3897</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4143</v>
+        <v>-2.1221</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5386</v>
+        <v>-1.2676</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2802</v>
@@ -2092,13 +2092,13 @@
         <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6714</v>
+        <v>0.2346</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1199</v>
+        <v>0.4121</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4485</v>
+        <v>-0.1775</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6093</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8821</v>
+        <v>-5.3332</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2829</v>
+        <v>-4.7884</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.5448</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9566</v>
@@ -2170,13 +2170,13 @@
         <v>1.9534</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5936</v>
+        <v>1.1425</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7981</v>
+        <v>0.2925</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7956</v>
+        <v>0.85</v>
       </c>
       <c r="V22" t="n">
         <v>-3.3238</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.167999999999998</v>
+        <v>5.8421</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.4826</v>
+        <v>-7.482600000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>12.6505</v>
+        <v>13.3246</v>
       </c>
       <c r="G23" t="n">
         <v>-0.299599999999999</v>
@@ -2248,13 +2248,13 @@
         <v>22.4644</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8342</v>
+        <v>3.5083</v>
       </c>
       <c r="T23" t="n">
         <v>1.7072</v>
       </c>
       <c r="U23" t="n">
-        <v>1.127</v>
+        <v>1.801</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2734</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484286_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484286_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.1646</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.2224</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.8279</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,11 +1130,16 @@
       <c r="X8" t="n">
         <v>-1.1638</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1172,12 +1212,17 @@
       </c>
       <c r="X9" t="n">
         <v>-0.5545</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1250,6 +1295,11 @@
       </c>
       <c r="X10" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-3.0466</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,47 +1462,48 @@
       <c r="X12" t="n">
         <v>-8.4236</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7119</v>
+        <v>3.884</v>
       </c>
       <c r="E13" t="n">
-        <v>2.379</v>
+        <v>0.551</v>
       </c>
       <c r="F13" t="n">
         <v>3.333</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3502</v>
+        <v>0.5223</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6889</v>
+        <v>1.075</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6613</v>
+        <v>-0.5527</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7101</v>
+        <v>-0.1178</v>
       </c>
       <c r="K13" t="n">
-        <v>2.397</v>
+        <v>1.7831</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6869</v>
+        <v>-1.9009</v>
       </c>
       <c r="M13" t="n">
         <v>0.6401</v>
@@ -1484,48 +1540,53 @@
       </c>
       <c r="X13" t="n">
         <v>-1.4959</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2684</v>
+        <v>3.0474</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2167</v>
+        <v>-1.0042</v>
       </c>
       <c r="F14" t="n">
         <v>4.0517</v>
       </c>
       <c r="G14" t="n">
-        <v>3.6458</v>
+        <v>2.4248</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1491</v>
+        <v>1.5352</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4966</v>
+        <v>0.8897</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7449</v>
+        <v>2.524</v>
       </c>
       <c r="K14" t="n">
-        <v>3.057</v>
+        <v>2.443</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6879</v>
+        <v>0.0809</v>
       </c>
       <c r="M14" t="n">
         <v>-0.0992</v>
@@ -1562,6 +1623,11 @@
       </c>
       <c r="X14" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1572,7 +1638,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1640,631 +1706,838 @@
       </c>
       <c r="X15" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4953</v>
+        <v>1.8279</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.2353</v>
+        <v>1.8279</v>
       </c>
       <c r="F16" t="n">
-        <v>3.7306</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7298</v>
+        <v>1.8279</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7701</v>
+        <v>0.614</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0403</v>
+        <v>1.214</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5608</v>
+        <v>1.8279</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0728</v>
+        <v>0.614</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.214</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.169</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8429</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6739000000000001</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.3208</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0531</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5292</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5239</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0549</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2029</v>
+        <v>1.4953</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5521</v>
+        <v>-2.2353</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3492</v>
+        <v>3.7306</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3426</v>
+        <v>-0.7298</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8439</v>
+        <v>-0.7701</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4986</v>
+        <v>0.0403</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6438</v>
+        <v>-0.5608</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1241</v>
+        <v>0.0728</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7679</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6988</v>
+        <v>-0.169</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.968</v>
+        <v>-0.8429</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2692</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>3.3208</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0406</v>
+        <v>1.0531</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.046</v>
+        <v>0.5292</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0054</v>
+        <v>0.5239</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4373</v>
+        <v>-0.0549</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.694</v>
+        <v>1.221</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2409</v>
+        <v>1.221</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9349</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5123</v>
+        <v>1.221</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8921</v>
+        <v>0.614</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6202</v>
+        <v>0.607</v>
       </c>
       <c r="J18" t="n">
-        <v>0.778</v>
+        <v>1.221</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.614</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>0.607</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7342</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1949</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5393</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1231</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3447</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2215</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. POCULL DURAN</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.22</v>
+        <v>1.2029</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2812</v>
+        <v>1.5521</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5013</v>
+        <v>-0.3492</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1314</v>
+        <v>-1.3426</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1312</v>
+        <v>-0.8439</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0002</v>
+        <v>-0.4986</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3479</v>
+        <v>-0.6438</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3479</v>
+        <v>0.1241</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.7679</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4793</v>
+        <v>-0.6988</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4792</v>
+        <v>-0.968</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0002</v>
+        <v>0.2692</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0653</v>
+        <v>-0.0406</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0667</v>
+        <v>-0.046</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0014</v>
+        <v>0.0054</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. RECIO PINOL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0913</v>
+        <v>0.694</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5455</v>
+        <v>-0.2409</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4542</v>
+        <v>0.9349</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0283</v>
+        <v>1.5123</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1829</v>
+        <v>0.8921</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2112</v>
+        <v>0.6202</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.1435</v>
+        <v>0.778</v>
       </c>
       <c r="K20" t="n">
-        <v>0.472</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.6155</v>
+        <v>0.0809</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1152</v>
+        <v>0.7342</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2891</v>
+        <v>0.1949</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4043</v>
+        <v>0.5393</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5395</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2608</v>
+        <v>0.1231</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.3447</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3688</v>
+        <v>-0.2215</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8865</v>
+        <v>-0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.0549</v>
+        <v>-0.3869</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8317</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>L. POCULL DURAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3897</v>
+        <v>-0.22</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1221</v>
+        <v>0.2812</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2676</v>
+        <v>-0.5013</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2802</v>
+        <v>-0.1314</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3203</v>
+        <v>-0.1312</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0401</v>
+        <v>-0.0002</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8182</v>
+        <v>0.3479</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.3479</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0984</v>
+        <v>-0.4793</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.098</v>
+        <v>-0.4792</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0004</v>
+        <v>-0.0002</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.7348</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2346</v>
+        <v>-0.0653</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4121</v>
+        <v>-0.0667</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1775</v>
+        <v>0.0014</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6093</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1638</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3332</v>
+        <v>-1.0913</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7884</v>
+        <v>-2.5455</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5448</v>
+        <v>1.4542</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9566</v>
+        <v>-2.0283</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6493</v>
+        <v>0.1829</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3073</v>
+        <v>-2.2112</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.9322</v>
+        <v>-2.1435</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8161</v>
+        <v>0.472</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.1161</v>
+        <v>-2.6155</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0245</v>
+        <v>0.1152</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.2891</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8087</v>
+        <v>0.4043</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9534</v>
+        <v>2.5395</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1425</v>
+        <v>0.2608</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2925</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.85</v>
+        <v>-0.3688</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.3238</v>
+        <v>-0.8865</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.3238</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-3.3897</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.1221</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-1.2676</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.2802</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.3203</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8182</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.7776999999999999</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.0984</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.098</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-2.7348</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.2346</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.1775</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.1638</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I. ISERN CASES</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-5.3332</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-4.7884</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.5448</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.9566</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.6493</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.3073</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-2.9322</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.8161</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-2.1161</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.0245</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.8332000000000001</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8087</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.1425</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-3.3238</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-3.3238</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484286_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>5.8421</v>
       </c>
-      <c r="E23" t="n">
-        <v>-7.482600000000001</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="E25" t="n">
+        <v>-7.4826</v>
+      </c>
+      <c r="F25" t="n">
         <v>13.3246</v>
       </c>
-      <c r="G23" t="n">
-        <v>-0.299599999999999</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.0475</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-1.3471</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.9440000000000004</v>
-      </c>
-      <c r="K23" t="n">
-        <v>7.682099999999998</v>
-      </c>
-      <c r="L23" t="n">
-        <v>-6.738100000000001</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="G25" t="n">
+        <v>-0.2996000000000008</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.0477</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.347</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.944100000000001</v>
+      </c>
+      <c r="K25" t="n">
+        <v>7.682199999999998</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-6.738099999999999</v>
+      </c>
+      <c r="M25" t="n">
         <v>-1.2438</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N25" t="n">
         <v>-6.6347</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O25" t="n">
         <v>5.3908</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P25" t="n">
         <v>3.9069</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q25" t="n">
         <v>-18.5576</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>22.4644</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>3.5083</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>1.7072</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>1.801</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V25" t="n">
         <v>-1.2734</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W25" t="n">
         <v>8.4237</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X25" t="n">
         <v>-9.697099999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
